--- a/artfynd/A 58547-2025 artfynd.xlsx
+++ b/artfynd/A 58547-2025 artfynd.xlsx
@@ -1476,32 +1476,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130104785</v>
+        <v>130104744</v>
       </c>
       <c r="B10" t="n">
-        <v>98831</v>
+        <v>97077</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633125</v>
+        <v>633208</v>
       </c>
       <c r="R10" t="n">
-        <v>6661041</v>
+        <v>6661035</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1547,11 +1547,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>17 30 buketter</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1578,7 +1573,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130104779</v>
+        <v>130104785</v>
       </c>
       <c r="B11" t="n">
         <v>98831</v>
@@ -1613,10 +1608,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>633176</v>
+        <v>633125</v>
       </c>
       <c r="R11" t="n">
-        <v>6661084</v>
+        <v>6661041</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1653,7 +1648,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>4 30 buketter</t>
+          <t>17 30 buketter</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1680,7 +1675,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130104778</v>
+        <v>130104779</v>
       </c>
       <c r="B12" t="n">
         <v>98831</v>
@@ -1715,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633177</v>
+        <v>633176</v>
       </c>
       <c r="R12" t="n">
-        <v>6661088</v>
+        <v>6661084</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1755,7 +1750,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>5 40 buketter</t>
+          <t>4 30 buketter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1782,32 +1777,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130104744</v>
+        <v>130104778</v>
       </c>
       <c r="B13" t="n">
-        <v>97077</v>
+        <v>98831</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1817,10 +1812,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>633208</v>
+        <v>633177</v>
       </c>
       <c r="R13" t="n">
-        <v>6661035</v>
+        <v>6661088</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1853,6 +1848,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>5 40 buketter</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2680,32 +2680,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130104755</v>
+        <v>130104770</v>
       </c>
       <c r="B22" t="n">
-        <v>97077</v>
+        <v>97702</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2715,10 +2715,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>633175</v>
+        <v>633197</v>
       </c>
       <c r="R22" t="n">
-        <v>6661029</v>
+        <v>6661030</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2777,32 +2777,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130104770</v>
+        <v>130104755</v>
       </c>
       <c r="B23" t="n">
-        <v>97702</v>
+        <v>97077</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2812,10 +2812,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>633197</v>
+        <v>633175</v>
       </c>
       <c r="R23" t="n">
-        <v>6661030</v>
+        <v>6661029</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>

--- a/artfynd/A 58547-2025 artfynd.xlsx
+++ b/artfynd/A 58547-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130104774</v>
+        <v>130104753</v>
       </c>
       <c r="B3" t="n">
-        <v>98831</v>
+        <v>97077</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633138</v>
+        <v>633188</v>
       </c>
       <c r="R3" t="n">
-        <v>6661112</v>
+        <v>6661075</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -843,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>8 15buketter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130104753</v>
+        <v>130104774</v>
       </c>
       <c r="B4" t="n">
-        <v>97077</v>
+        <v>98831</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>633188</v>
+        <v>633138</v>
       </c>
       <c r="R4" t="n">
-        <v>6661075</v>
+        <v>6661112</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -945,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>8 15buketter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1476,32 +1476,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130104744</v>
+        <v>130104785</v>
       </c>
       <c r="B10" t="n">
-        <v>97077</v>
+        <v>98831</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633208</v>
+        <v>633125</v>
       </c>
       <c r="R10" t="n">
-        <v>6661035</v>
+        <v>6661041</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1547,6 +1547,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>17 30 buketter</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1573,7 +1578,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130104785</v>
+        <v>130104779</v>
       </c>
       <c r="B11" t="n">
         <v>98831</v>
@@ -1608,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>633125</v>
+        <v>633176</v>
       </c>
       <c r="R11" t="n">
-        <v>6661041</v>
+        <v>6661084</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1648,7 +1653,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>17 30 buketter</t>
+          <t>4 30 buketter</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1675,7 +1680,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130104779</v>
+        <v>130104778</v>
       </c>
       <c r="B12" t="n">
         <v>98831</v>
@@ -1710,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633176</v>
+        <v>633177</v>
       </c>
       <c r="R12" t="n">
-        <v>6661084</v>
+        <v>6661088</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1750,7 +1755,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>4 30 buketter</t>
+          <t>5 40 buketter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1777,32 +1782,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130104778</v>
+        <v>130104744</v>
       </c>
       <c r="B13" t="n">
-        <v>98831</v>
+        <v>97077</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1812,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>633177</v>
+        <v>633208</v>
       </c>
       <c r="R13" t="n">
-        <v>6661088</v>
+        <v>6661035</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1848,11 +1853,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>5 40 buketter</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2486,10 +2486,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130104754</v>
+        <v>130104764</v>
       </c>
       <c r="B20" t="n">
-        <v>97077</v>
+        <v>57738</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2497,21 +2497,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2521,10 +2521,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>633178</v>
+        <v>633190</v>
       </c>
       <c r="R20" t="n">
-        <v>6661028</v>
+        <v>6661058</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2583,10 +2583,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130104764</v>
+        <v>130104754</v>
       </c>
       <c r="B21" t="n">
-        <v>57738</v>
+        <v>97077</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2594,21 +2594,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2618,10 +2618,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>633190</v>
+        <v>633178</v>
       </c>
       <c r="R21" t="n">
-        <v>6661058</v>
+        <v>6661028</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>

--- a/artfynd/A 58547-2025 artfynd.xlsx
+++ b/artfynd/A 58547-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130104748</v>
       </c>
       <c r="B2" t="n">
-        <v>97077</v>
+        <v>97079</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130104753</v>
       </c>
       <c r="B3" t="n">
-        <v>97077</v>
+        <v>97079</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130104774</v>
       </c>
       <c r="B4" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>130104775</v>
       </c>
       <c r="B5" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>130104781</v>
       </c>
       <c r="B6" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>130104782</v>
       </c>
       <c r="B7" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>130104776</v>
       </c>
       <c r="B8" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>130104749</v>
       </c>
       <c r="B9" t="n">
-        <v>97077</v>
+        <v>97079</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>130104785</v>
       </c>
       <c r="B10" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>130104779</v>
       </c>
       <c r="B11" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         <v>130104778</v>
       </c>
       <c r="B12" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>130104744</v>
       </c>
       <c r="B13" t="n">
-        <v>97077</v>
+        <v>97079</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>130104756</v>
       </c>
       <c r="B14" t="n">
-        <v>91603</v>
+        <v>91605</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>130104787</v>
       </c>
       <c r="B15" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>130104777</v>
       </c>
       <c r="B16" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>130104783</v>
       </c>
       <c r="B17" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>130104773</v>
       </c>
       <c r="B18" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>130104784</v>
       </c>
       <c r="B19" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2486,10 +2486,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130104764</v>
+        <v>130104754</v>
       </c>
       <c r="B20" t="n">
-        <v>57738</v>
+        <v>97079</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2497,21 +2497,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2521,10 +2521,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>633190</v>
+        <v>633178</v>
       </c>
       <c r="R20" t="n">
-        <v>6661058</v>
+        <v>6661028</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2583,10 +2583,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130104754</v>
+        <v>130104764</v>
       </c>
       <c r="B21" t="n">
-        <v>97077</v>
+        <v>57738</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2594,21 +2594,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2618,10 +2618,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>633178</v>
+        <v>633190</v>
       </c>
       <c r="R21" t="n">
-        <v>6661028</v>
+        <v>6661058</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2683,7 +2683,7 @@
         <v>130104770</v>
       </c>
       <c r="B22" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>130104755</v>
       </c>
       <c r="B23" t="n">
-        <v>97077</v>
+        <v>97079</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>130104780</v>
       </c>
       <c r="B24" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>130104788</v>
       </c>
       <c r="B25" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3078,32 +3078,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130104797</v>
+        <v>130104790</v>
       </c>
       <c r="B26" t="n">
-        <v>8440</v>
+        <v>98833</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3113,10 +3113,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>633176</v>
+        <v>633112</v>
       </c>
       <c r="R26" t="n">
-        <v>6661083</v>
+        <v>6661079</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3149,6 +3149,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>11 12 buketter</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3175,32 +3180,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130104790</v>
+        <v>130104797</v>
       </c>
       <c r="B27" t="n">
-        <v>98831</v>
+        <v>8440</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3210,10 +3215,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>633112</v>
+        <v>633176</v>
       </c>
       <c r="R27" t="n">
-        <v>6661079</v>
+        <v>6661083</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3246,11 +3251,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>11 12 buketter</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3280,7 +3280,7 @@
         <v>130104786</v>
       </c>
       <c r="B28" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 58547-2025 artfynd.xlsx
+++ b/artfynd/A 58547-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130104748</v>
       </c>
       <c r="B2" t="n">
-        <v>97079</v>
+        <v>97166</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130104753</v>
       </c>
       <c r="B3" t="n">
-        <v>97079</v>
+        <v>97166</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130104774</v>
       </c>
       <c r="B4" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>130104775</v>
       </c>
       <c r="B5" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>130104781</v>
       </c>
       <c r="B6" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>130104782</v>
       </c>
       <c r="B7" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
         <v>130104776</v>
       </c>
       <c r="B8" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>130104749</v>
       </c>
       <c r="B9" t="n">
-        <v>97079</v>
+        <v>97166</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         <v>130104785</v>
       </c>
       <c r="B10" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1578,32 +1578,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130104779</v>
+        <v>130104744</v>
       </c>
       <c r="B11" t="n">
-        <v>98833</v>
+        <v>97166</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>633176</v>
+        <v>633208</v>
       </c>
       <c r="R11" t="n">
-        <v>6661084</v>
+        <v>6661035</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1649,11 +1649,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>4 30 buketter</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1680,10 +1675,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130104778</v>
+        <v>130104779</v>
       </c>
       <c r="B12" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1715,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633177</v>
+        <v>633176</v>
       </c>
       <c r="R12" t="n">
-        <v>6661088</v>
+        <v>6661084</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1755,7 +1750,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>5 40 buketter</t>
+          <t>4 30 buketter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1782,32 +1777,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130104744</v>
+        <v>130104778</v>
       </c>
       <c r="B13" t="n">
-        <v>97079</v>
+        <v>98920</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1817,10 +1812,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>633208</v>
+        <v>633177</v>
       </c>
       <c r="R13" t="n">
-        <v>6661035</v>
+        <v>6661088</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1853,6 +1848,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>5 40 buketter</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1882,7 +1882,7 @@
         <v>130104756</v>
       </c>
       <c r="B14" t="n">
-        <v>91605</v>
+        <v>91692</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>130104787</v>
       </c>
       <c r="B15" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>130104777</v>
       </c>
       <c r="B16" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>130104783</v>
       </c>
       <c r="B17" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>130104773</v>
       </c>
       <c r="B18" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>130104784</v>
       </c>
       <c r="B19" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2486,10 +2486,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130104754</v>
+        <v>130104764</v>
       </c>
       <c r="B20" t="n">
-        <v>97079</v>
+        <v>57823</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2497,21 +2497,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2521,10 +2521,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>633178</v>
+        <v>633190</v>
       </c>
       <c r="R20" t="n">
-        <v>6661028</v>
+        <v>6661058</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2583,10 +2583,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130104764</v>
+        <v>130104754</v>
       </c>
       <c r="B21" t="n">
-        <v>57738</v>
+        <v>97166</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2594,21 +2594,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2618,10 +2618,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>633190</v>
+        <v>633178</v>
       </c>
       <c r="R21" t="n">
-        <v>6661058</v>
+        <v>6661028</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2683,7 +2683,7 @@
         <v>130104770</v>
       </c>
       <c r="B22" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2780,7 +2780,7 @@
         <v>130104755</v>
       </c>
       <c r="B23" t="n">
-        <v>97079</v>
+        <v>97166</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>130104780</v>
       </c>
       <c r="B24" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2979,7 +2979,7 @@
         <v>130104788</v>
       </c>
       <c r="B25" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3078,32 +3078,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130104790</v>
+        <v>130104797</v>
       </c>
       <c r="B26" t="n">
-        <v>98833</v>
+        <v>8440</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3113,10 +3113,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>633112</v>
+        <v>633176</v>
       </c>
       <c r="R26" t="n">
-        <v>6661079</v>
+        <v>6661083</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3149,11 +3149,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>11 12 buketter</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3180,32 +3175,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130104797</v>
+        <v>130104790</v>
       </c>
       <c r="B27" t="n">
-        <v>8440</v>
+        <v>98920</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3215,10 +3210,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>633176</v>
+        <v>633112</v>
       </c>
       <c r="R27" t="n">
-        <v>6661083</v>
+        <v>6661079</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3251,6 +3246,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>11 12 buketter</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3280,7 +3280,7 @@
         <v>130104786</v>
       </c>
       <c r="B28" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 58547-2025 artfynd.xlsx
+++ b/artfynd/A 58547-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130104753</v>
+        <v>130104774</v>
       </c>
       <c r="B3" t="n">
-        <v>97166</v>
+        <v>98920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633188</v>
+        <v>633138</v>
       </c>
       <c r="R3" t="n">
-        <v>6661075</v>
+        <v>6661112</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -843,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>8 15buketter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130104774</v>
+        <v>130104753</v>
       </c>
       <c r="B4" t="n">
-        <v>98920</v>
+        <v>97166</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>633138</v>
+        <v>633188</v>
       </c>
       <c r="R4" t="n">
-        <v>6661112</v>
+        <v>6661075</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -940,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>8 15buketter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -2680,32 +2680,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130104770</v>
+        <v>130104755</v>
       </c>
       <c r="B22" t="n">
-        <v>97791</v>
+        <v>97166</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2715,10 +2715,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>633197</v>
+        <v>633175</v>
       </c>
       <c r="R22" t="n">
-        <v>6661030</v>
+        <v>6661029</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2777,32 +2777,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130104755</v>
+        <v>130104770</v>
       </c>
       <c r="B23" t="n">
-        <v>97166</v>
+        <v>97791</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2812,10 +2812,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>633175</v>
+        <v>633197</v>
       </c>
       <c r="R23" t="n">
-        <v>6661029</v>
+        <v>6661030</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>

--- a/artfynd/A 58547-2025 artfynd.xlsx
+++ b/artfynd/A 58547-2025 artfynd.xlsx
@@ -2680,32 +2680,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130104755</v>
+        <v>130104770</v>
       </c>
       <c r="B22" t="n">
-        <v>97166</v>
+        <v>97791</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2715,10 +2715,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>633175</v>
+        <v>633197</v>
       </c>
       <c r="R22" t="n">
-        <v>6661029</v>
+        <v>6661030</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2777,32 +2777,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130104770</v>
+        <v>130104755</v>
       </c>
       <c r="B23" t="n">
-        <v>97791</v>
+        <v>97166</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2812,10 +2812,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>633197</v>
+        <v>633175</v>
       </c>
       <c r="R23" t="n">
-        <v>6661030</v>
+        <v>6661029</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>

--- a/artfynd/A 58547-2025 artfynd.xlsx
+++ b/artfynd/A 58547-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130104774</v>
+        <v>130104753</v>
       </c>
       <c r="B3" t="n">
-        <v>98920</v>
+        <v>97166</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633138</v>
+        <v>633188</v>
       </c>
       <c r="R3" t="n">
-        <v>6661112</v>
+        <v>6661075</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -843,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>8 15buketter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130104753</v>
+        <v>130104774</v>
       </c>
       <c r="B4" t="n">
-        <v>97166</v>
+        <v>98920</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>633188</v>
+        <v>633138</v>
       </c>
       <c r="R4" t="n">
-        <v>6661075</v>
+        <v>6661112</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -945,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>8 15buketter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1476,32 +1476,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130104744</v>
+        <v>130104779</v>
       </c>
       <c r="B10" t="n">
-        <v>97166</v>
+        <v>98920</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633208</v>
+        <v>633176</v>
       </c>
       <c r="R10" t="n">
-        <v>6661035</v>
+        <v>6661084</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1547,6 +1547,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>4 30 buketter</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1573,7 +1578,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130104778</v>
+        <v>130104785</v>
       </c>
       <c r="B11" t="n">
         <v>98920</v>
@@ -1608,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>633177</v>
+        <v>633125</v>
       </c>
       <c r="R11" t="n">
-        <v>6661088</v>
+        <v>6661041</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1648,7 +1653,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>5 40 buketter</t>
+          <t>17 30 buketter</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1675,32 +1680,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130104779</v>
+        <v>130104744</v>
       </c>
       <c r="B12" t="n">
-        <v>98920</v>
+        <v>97166</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1710,10 +1715,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633176</v>
+        <v>633208</v>
       </c>
       <c r="R12" t="n">
-        <v>6661084</v>
+        <v>6661035</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1746,11 +1751,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>4 30 buketter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1777,7 +1777,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130104785</v>
+        <v>130104778</v>
       </c>
       <c r="B13" t="n">
         <v>98920</v>
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>633125</v>
+        <v>633177</v>
       </c>
       <c r="R13" t="n">
-        <v>6661041</v>
+        <v>6661088</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>17 30 buketter</t>
+          <t>5 40 buketter</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 58547-2025 artfynd.xlsx
+++ b/artfynd/A 58547-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130104748</v>
       </c>
       <c r="B2" t="n">
-        <v>97166</v>
+        <v>97169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>130104753</v>
       </c>
       <c r="B3" t="n">
-        <v>97166</v>
+        <v>97169</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>130104774</v>
       </c>
       <c r="B4" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>130104775</v>
       </c>
       <c r="B5" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1073,10 +1073,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130104782</v>
+        <v>130104781</v>
       </c>
       <c r="B6" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>633186</v>
+        <v>633206</v>
       </c>
       <c r="R6" t="n">
         <v>6661062</v>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2 5 buketter</t>
+          <t>20 20 buketter</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,10 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130104781</v>
+        <v>130104782</v>
       </c>
       <c r="B7" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>633206</v>
+        <v>633186</v>
       </c>
       <c r="R7" t="n">
         <v>6661062</v>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>20 20 buketter</t>
+          <t>2 5 buketter</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1280,7 +1280,7 @@
         <v>130104776</v>
       </c>
       <c r="B8" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
         <v>130104749</v>
       </c>
       <c r="B9" t="n">
-        <v>97166</v>
+        <v>97169</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,32 +1476,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130104779</v>
+        <v>130104744</v>
       </c>
       <c r="B10" t="n">
-        <v>98920</v>
+        <v>97169</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633176</v>
+        <v>633208</v>
       </c>
       <c r="R10" t="n">
-        <v>6661084</v>
+        <v>6661035</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1547,11 +1547,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>4 30 buketter</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1581,7 +1576,7 @@
         <v>130104785</v>
       </c>
       <c r="B11" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1680,32 +1675,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130104744</v>
+        <v>130104779</v>
       </c>
       <c r="B12" t="n">
-        <v>97166</v>
+        <v>98923</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1715,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633208</v>
+        <v>633176</v>
       </c>
       <c r="R12" t="n">
-        <v>6661035</v>
+        <v>6661084</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1751,6 +1746,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>4 30 buketter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1780,7 +1780,7 @@
         <v>130104778</v>
       </c>
       <c r="B13" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>130104756</v>
       </c>
       <c r="B14" t="n">
-        <v>91692</v>
+        <v>91695</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1976,10 +1976,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130104777</v>
+        <v>130104787</v>
       </c>
       <c r="B15" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>633190</v>
+        <v>633138</v>
       </c>
       <c r="R15" t="n">
-        <v>6661077</v>
+        <v>6661052</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>1 6 buketter</t>
+          <t>14 50 buketter</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2078,10 +2078,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130104787</v>
+        <v>130104777</v>
       </c>
       <c r="B16" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>633138</v>
+        <v>633190</v>
       </c>
       <c r="R16" t="n">
-        <v>6661052</v>
+        <v>6661077</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2153,7 +2153,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>14 50 buketter</t>
+          <t>1 6 buketter</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2183,7 +2183,7 @@
         <v>130104783</v>
       </c>
       <c r="B17" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2285,7 +2285,7 @@
         <v>130104773</v>
       </c>
       <c r="B18" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>130104784</v>
       </c>
       <c r="B19" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>130104754</v>
       </c>
       <c r="B20" t="n">
-        <v>97166</v>
+        <v>97169</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2680,32 +2680,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130104770</v>
+        <v>130104755</v>
       </c>
       <c r="B22" t="n">
-        <v>97791</v>
+        <v>97169</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2715,10 +2715,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>633197</v>
+        <v>633175</v>
       </c>
       <c r="R22" t="n">
-        <v>6661030</v>
+        <v>6661029</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2777,32 +2777,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130104755</v>
+        <v>130104770</v>
       </c>
       <c r="B23" t="n">
-        <v>97166</v>
+        <v>97794</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2812,10 +2812,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>633175</v>
+        <v>633197</v>
       </c>
       <c r="R23" t="n">
-        <v>6661029</v>
+        <v>6661030</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2874,10 +2874,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130104788</v>
+        <v>130104780</v>
       </c>
       <c r="B24" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2909,10 +2909,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>633135</v>
+        <v>633183</v>
       </c>
       <c r="R24" t="n">
-        <v>6661061</v>
+        <v>6661074</v>
       </c>
       <c r="S24" t="n">
         <v>1</v>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>13 60 buketter</t>
+          <t>3 10 buketter</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2976,10 +2976,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130104780</v>
+        <v>130104788</v>
       </c>
       <c r="B25" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3011,10 +3011,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>633183</v>
+        <v>633135</v>
       </c>
       <c r="R25" t="n">
-        <v>6661074</v>
+        <v>6661061</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>3 10 buketter</t>
+          <t>13 60 buketter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3178,7 +3178,7 @@
         <v>130104790</v>
       </c>
       <c r="B27" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>130104786</v>
       </c>
       <c r="B28" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 58547-2025 artfynd.xlsx
+++ b/artfynd/A 58547-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3377,6 +3377,345 @@
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>132867726</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99119</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Långmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>633219</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6661053</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>132867725</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99119</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Långmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>633205</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6661054</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>132867731</v>
+      </c>
+      <c r="B31" t="n">
+        <v>97359</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>53</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Långmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>633211</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6661035</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>17:13</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58547-2025 artfynd.xlsx
+++ b/artfynd/A 58547-2025 artfynd.xlsx
@@ -3382,7 +3382,7 @@
         <v>132867726</v>
       </c>
       <c r="B29" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>132867725</v>
       </c>
       <c r="B30" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>132867731</v>
       </c>
       <c r="B31" t="n">
-        <v>97359</v>
+        <v>97361</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 58547-2025 artfynd.xlsx
+++ b/artfynd/A 58547-2025 artfynd.xlsx
@@ -3382,7 +3382,7 @@
         <v>132867726</v>
       </c>
       <c r="B29" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
         <v>132867725</v>
       </c>
       <c r="B30" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
         <v>132867731</v>
       </c>
       <c r="B31" t="n">
-        <v>97361</v>
+        <v>97362</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 58547-2025 artfynd.xlsx
+++ b/artfynd/A 58547-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130104748</v>
+        <v>130104744</v>
       </c>
       <c r="B2" t="n">
-        <v>97169</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>633164</v>
+        <v>633208</v>
       </c>
       <c r="R2" t="n">
-        <v>6661043</v>
+        <v>6661035</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130104753</v>
+        <v>130104746</v>
       </c>
       <c r="B3" t="n">
-        <v>97169</v>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633188</v>
+        <v>633246</v>
       </c>
       <c r="R3" t="n">
-        <v>6661075</v>
+        <v>6661031</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -832,7 +832,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Bälinge</t>
+          <t>Skuttunge</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130104774</v>
+        <v>130104748</v>
       </c>
       <c r="B4" t="n">
-        <v>98923</v>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>633138</v>
+        <v>633164</v>
       </c>
       <c r="R4" t="n">
-        <v>6661112</v>
+        <v>6661043</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -940,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>8 15buketter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -971,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130104775</v>
+        <v>130104749</v>
       </c>
       <c r="B5" t="n">
-        <v>98923</v>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>633145</v>
+        <v>633136</v>
       </c>
       <c r="R5" t="n">
-        <v>6661110</v>
+        <v>6661051</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1042,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>7 5 buketter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130104781</v>
+        <v>130104752</v>
       </c>
       <c r="B6" t="n">
-        <v>98923</v>
+        <v>97358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>633206</v>
+        <v>633144</v>
       </c>
       <c r="R6" t="n">
-        <v>6661062</v>
+        <v>6661136</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1144,11 +1134,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>20 20 buketter</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1175,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130104782</v>
+        <v>130104753</v>
       </c>
       <c r="B7" t="n">
-        <v>98923</v>
+        <v>97358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>633186</v>
+        <v>633188</v>
       </c>
       <c r="R7" t="n">
-        <v>6661062</v>
+        <v>6661075</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1246,11 +1231,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2 5 buketter</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1277,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130104776</v>
+        <v>130104754</v>
       </c>
       <c r="B8" t="n">
-        <v>98923</v>
+        <v>97358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1312,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>633154</v>
+        <v>633178</v>
       </c>
       <c r="R8" t="n">
-        <v>6661109</v>
+        <v>6661028</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1348,11 +1328,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>6 15 buketter</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1379,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130104749</v>
+        <v>130104755</v>
       </c>
       <c r="B9" t="n">
-        <v>97169</v>
+        <v>97358</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1414,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>633136</v>
+        <v>633175</v>
       </c>
       <c r="R9" t="n">
-        <v>6661051</v>
+        <v>6661029</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1476,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130104744</v>
+        <v>132867731</v>
       </c>
       <c r="B10" t="n">
-        <v>97169</v>
+        <v>97435</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,17 +1482,17 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långmossen N, Upl</t>
+          <t>Långmossen, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>633208</v>
+        <v>633211</v>
       </c>
       <c r="R10" t="n">
         <v>6661035</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1541,12 +1516,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-12-12</t>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1573,32 +1558,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130104785</v>
+        <v>130104766</v>
       </c>
       <c r="B11" t="n">
-        <v>98923</v>
+        <v>91680</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>3215</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1608,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>633125</v>
+        <v>633217</v>
       </c>
       <c r="R11" t="n">
-        <v>6661041</v>
+        <v>6661104</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1633,7 +1618,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Bälinge</t>
+          <t>Skuttunge</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1644,11 +1629,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>17 30 buketter</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1675,32 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130104779</v>
+        <v>130104756</v>
       </c>
       <c r="B12" t="n">
-        <v>98923</v>
+        <v>91872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1710,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>633176</v>
+        <v>633136</v>
       </c>
       <c r="R12" t="n">
-        <v>6661084</v>
+        <v>6661051</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1746,11 +1726,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>4 30 buketter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1777,32 +1752,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130104778</v>
+        <v>130104761</v>
       </c>
       <c r="B13" t="n">
-        <v>98923</v>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1812,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>633177</v>
+        <v>633122</v>
       </c>
       <c r="R13" t="n">
-        <v>6661088</v>
+        <v>6661132</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1848,11 +1823,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>5 40 buketter</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1879,10 +1849,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130104756</v>
+        <v>130104763</v>
       </c>
       <c r="B14" t="n">
-        <v>91695</v>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1890,21 +1860,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1914,10 +1884,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>633136</v>
+        <v>633102</v>
       </c>
       <c r="R14" t="n">
-        <v>6661051</v>
+        <v>6661087</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -1976,32 +1946,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130104787</v>
+        <v>130104764</v>
       </c>
       <c r="B15" t="n">
-        <v>98923</v>
+        <v>57950</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2011,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>633138</v>
+        <v>633190</v>
       </c>
       <c r="R15" t="n">
-        <v>6661052</v>
+        <v>6661058</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2047,11 +2017,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>14 50 buketter</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2078,32 +2043,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130104777</v>
+        <v>130104797</v>
       </c>
       <c r="B16" t="n">
-        <v>98923</v>
+        <v>8444</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>106554</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2113,10 +2078,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>633190</v>
+        <v>633176</v>
       </c>
       <c r="R16" t="n">
-        <v>6661077</v>
+        <v>6661083</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2149,11 +2114,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>1 6 buketter</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2180,10 +2140,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130104783</v>
+        <v>130104773</v>
       </c>
       <c r="B17" t="n">
-        <v>98923</v>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2215,10 +2175,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>633213</v>
+        <v>633133</v>
       </c>
       <c r="R17" t="n">
-        <v>6661055</v>
+        <v>6661098</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2255,7 +2215,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>19 25 buketter</t>
+          <t>9 20 buketter</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2282,10 +2242,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130104773</v>
+        <v>130104774</v>
       </c>
       <c r="B18" t="n">
-        <v>98923</v>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2317,10 +2277,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>633133</v>
+        <v>633138</v>
       </c>
       <c r="R18" t="n">
-        <v>6661098</v>
+        <v>6661112</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2357,7 +2317,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>9 20 buketter</t>
+          <t>8 15buketter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2384,10 +2344,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130104784</v>
+        <v>130104775</v>
       </c>
       <c r="B19" t="n">
-        <v>98923</v>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2419,10 +2379,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>633142</v>
+        <v>633145</v>
       </c>
       <c r="R19" t="n">
-        <v>6661039</v>
+        <v>6661110</v>
       </c>
       <c r="S19" t="n">
         <v>1</v>
@@ -2459,7 +2419,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>18 8 buketter</t>
+          <t>7 5 buketter</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2486,32 +2446,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130104754</v>
+        <v>130104776</v>
       </c>
       <c r="B20" t="n">
-        <v>97169</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2521,10 +2481,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>633178</v>
+        <v>633154</v>
       </c>
       <c r="R20" t="n">
-        <v>6661028</v>
+        <v>6661109</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
@@ -2557,6 +2517,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>6 15 buketter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2583,32 +2548,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130104764</v>
+        <v>130104777</v>
       </c>
       <c r="B21" t="n">
-        <v>57823</v>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2621,7 +2586,7 @@
         <v>633190</v>
       </c>
       <c r="R21" t="n">
-        <v>6661058</v>
+        <v>6661077</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
@@ -2654,6 +2619,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>1 6 buketter</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2680,32 +2650,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130104755</v>
+        <v>130104778</v>
       </c>
       <c r="B22" t="n">
-        <v>97169</v>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2715,10 +2685,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>633175</v>
+        <v>633177</v>
       </c>
       <c r="R22" t="n">
-        <v>6661029</v>
+        <v>6661088</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
@@ -2751,6 +2721,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>5 40 buketter</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2777,32 +2752,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130104770</v>
+        <v>130104779</v>
       </c>
       <c r="B23" t="n">
-        <v>97794</v>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2812,10 +2787,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>633197</v>
+        <v>633176</v>
       </c>
       <c r="R23" t="n">
-        <v>6661030</v>
+        <v>6661084</v>
       </c>
       <c r="S23" t="n">
         <v>1</v>
@@ -2848,6 +2823,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>4 30 buketter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2877,7 +2857,7 @@
         <v>130104780</v>
       </c>
       <c r="B24" t="n">
-        <v>98923</v>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2976,10 +2956,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130104788</v>
+        <v>130104781</v>
       </c>
       <c r="B25" t="n">
-        <v>98923</v>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3011,10 +2991,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>633135</v>
+        <v>633206</v>
       </c>
       <c r="R25" t="n">
-        <v>6661061</v>
+        <v>6661062</v>
       </c>
       <c r="S25" t="n">
         <v>1</v>
@@ -3051,7 +3031,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>13 60 buketter</t>
+          <t>20 20 buketter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3078,32 +3058,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130104797</v>
+        <v>130104782</v>
       </c>
       <c r="B26" t="n">
-        <v>8440</v>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106554</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3113,10 +3093,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>633176</v>
+        <v>633186</v>
       </c>
       <c r="R26" t="n">
-        <v>6661083</v>
+        <v>6661062</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3149,6 +3129,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>2 5 buketter</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3175,10 +3160,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130104790</v>
+        <v>130104783</v>
       </c>
       <c r="B27" t="n">
-        <v>98923</v>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3210,10 +3195,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>633112</v>
+        <v>633213</v>
       </c>
       <c r="R27" t="n">
-        <v>6661079</v>
+        <v>6661055</v>
       </c>
       <c r="S27" t="n">
         <v>1</v>
@@ -3250,7 +3235,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>11 12 buketter</t>
+          <t>19 25 buketter</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3277,10 +3262,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130104786</v>
+        <v>130104784</v>
       </c>
       <c r="B28" t="n">
-        <v>98923</v>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3312,10 +3297,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>633136</v>
+        <v>633142</v>
       </c>
       <c r="R28" t="n">
-        <v>6661051</v>
+        <v>6661039</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
@@ -3352,7 +3337,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>15 10 buketter</t>
+          <t>18 8 buketter</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3379,10 +3364,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132867726</v>
+        <v>130104785</v>
       </c>
       <c r="B29" t="n">
-        <v>99132</v>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3407,29 +3392,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Långmossen, Upl</t>
+          <t>Långmossen N, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>633219</v>
+        <v>633125</v>
       </c>
       <c r="R29" t="n">
-        <v>6661053</v>
+        <v>6661041</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3453,22 +3429,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>16:19</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>16:19</t>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>17 30 buketter</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3495,10 +3466,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132867725</v>
+        <v>130104786</v>
       </c>
       <c r="B30" t="n">
-        <v>99132</v>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3523,29 +3494,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Långmossen, Upl</t>
+          <t>Långmossen N, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>633205</v>
+        <v>633136</v>
       </c>
       <c r="R30" t="n">
-        <v>6661054</v>
+        <v>6661051</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3569,22 +3531,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>16:15</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>16:15</t>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>15 10 buketter</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3611,48 +3568,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132867731</v>
+        <v>130104787</v>
       </c>
       <c r="B31" t="n">
-        <v>97372</v>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Långmossen, Upl</t>
+          <t>Långmossen N, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>633211</v>
+        <v>633138</v>
       </c>
       <c r="R31" t="n">
-        <v>6661035</v>
+        <v>6661052</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3676,22 +3633,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>17:13</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>17:13</t>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>14 50 buketter</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3715,6 +3667,840 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>130104788</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Långmossen N, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>633135</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6661061</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>13 60 buketter</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>130104789</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Långmossen N, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>633098</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6661062</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>12 12 buketter</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>130104790</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Långmossen N, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>633112</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6661079</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>11 12 buketter</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>130104791</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Långmossen N, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>633109</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6661106</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>10 5 buketter</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>132867725</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Långmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>633205</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6661054</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>132867726</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Långmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>633219</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6661053</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>130104770</v>
+      </c>
+      <c r="B38" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Långmossen N, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>633197</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6661030</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>130104772</v>
+      </c>
+      <c r="B39" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Långmossen N, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>633193</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6661012</v>
+      </c>
+      <c r="S39" t="n">
+        <v>1</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
